--- a/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,0%</t>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -673,9 +673,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 264,00</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,5%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▲ 8,7%</t>
+          <t>▲ 10,3%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 212,00</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▲ 53,3%</t>
+          <t>▲ 81,2%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -962,8 +962,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -972,37 +974,39 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1031,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>▼ 85,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>16</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1074,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,7 +1104,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1108,10 +1112,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1120,39 +1122,37 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1177,25 +1177,25 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 714,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 264,00</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▲ 8,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1258,10 +1258,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1270,39 +1268,37 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1327,33 +1323,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 212,00</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>23</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 53,3%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1370,12 +1366,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1400,7 +1396,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1408,10 +1404,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1420,39 +1414,37 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1477,33 +1469,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 106,00</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 85,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>15</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1520,12 +1512,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1597,12 +1589,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1627,7 +1619,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 584,00</t>
+          <t>R$ 714,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1636,24 +1628,24 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>15</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1670,12 +1662,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1747,12 +1739,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1786,11 +1778,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,5%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1820,12 +1812,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1897,12 +1889,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1930,17 +1922,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▲ 45,5%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1970,12 +1962,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2047,12 +2039,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2077,33 +2069,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 584,00</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2120,12 +2112,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2197,12 +2189,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2227,7 +2219,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2236,24 +2228,24 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,1%</t>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2270,12 +2262,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2347,12 +2339,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2386,11 +2378,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,2%</t>
+        <v>16</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 45,5%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2420,12 +2412,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2497,12 +2489,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2530,9 +2522,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
@@ -2540,7 +2532,7 @@
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>▲ 83,3%</t>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2570,12 +2562,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2647,12 +2639,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2677,7 +2669,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2686,24 +2678,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2720,12 +2712,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2797,12 +2789,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2830,17 +2822,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,5%</t>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,2%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2870,12 +2862,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2947,12 +2939,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2977,7 +2969,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2986,24 +2978,24 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>11</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3020,12 +3012,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3097,12 +3089,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3136,11 +3128,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3170,12 +3162,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3247,12 +3239,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3286,11 +3278,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3320,12 +3312,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3397,12 +3389,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3436,16 +3428,16 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
@@ -3470,12 +3462,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3547,12 +3539,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3586,11 +3578,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3620,12 +3612,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3697,12 +3689,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3730,17 +3722,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3770,12 +3762,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3847,12 +3839,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3877,7 +3869,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3886,11 +3878,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3899,11 +3891,11 @@
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3920,12 +3912,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3997,12 +3989,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4036,11 +4028,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4070,12 +4062,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4147,12 +4139,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4180,17 +4172,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4220,12 +4212,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4297,12 +4289,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4327,7 +4319,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 175,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4336,24 +4328,24 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 114,3%</t>
+        <v>9</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4370,12 +4362,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4447,12 +4439,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4480,17 +4472,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4520,12 +4512,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4597,12 +4589,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4627,33 +4619,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>▼ 53,3%</t>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4670,12 +4662,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4700,7 +4692,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4708,8 +4700,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>0</v>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4718,37 +4712,39 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4773,7 +4769,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 175,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4784,22 +4780,22 @@
       <c r="I58" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,1%</t>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4816,12 +4812,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4846,7 +4842,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4854,47 +4850,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4922,17 +4922,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 35,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -5000,8 +5000,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>1</v>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -5010,37 +5012,39 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5065,33 +5069,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,7%</t>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5108,12 +5112,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5138,7 +5142,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5146,10 +5150,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5158,39 +5160,37 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5226,9 +5226,9 @@
       <c r="I64" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5296,51 +5296,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5374,11 +5370,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>19</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5408,12 +5404,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5438,7 +5434,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5446,10 +5442,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I67" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5458,39 +5452,37 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5518,17 +5510,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 250,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5558,12 +5550,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5635,12 +5627,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5665,33 +5657,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5708,12 +5700,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5785,12 +5777,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5815,7 +5807,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5824,24 +5816,24 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5858,12 +5850,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5935,12 +5927,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5968,17 +5960,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+        <v>7</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6008,12 +6000,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6085,12 +6077,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6115,33 +6107,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6158,82 +6150,532 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>UTD-027-BR</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Porta Talheres Extensivel Branco</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>6421065554</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,8%</t>
+          <t>▼ 38,5%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -673,9 +673,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -744,24 +744,24 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,3%</t>
+        <v>26</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -886,20 +886,20 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▲ 81,2%</t>
+          <t>▲ 10,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
@@ -907,7 +907,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -954,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -962,10 +962,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -974,41 +972,39 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1031,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,0%</t>
+        <v>29</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 81,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1074,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1104,7 +1100,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1112,8 +1108,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1122,39 +1120,41 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1177,33 +1177,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 264,00</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,5%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,7%</t>
+        <v>16</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1293,14 +1293,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 212,00</t>
+          <t>R$ 264,00</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 24,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▲ 53,3%</t>
+          <t>▲ 8,7%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1366,12 +1366,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1439,14 +1439,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1469,33 +1469,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 85,2%</t>
+          <t>R$ 212,00</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>23</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 53,3%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1512,14 +1512,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1550,10 +1550,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1562,41 +1560,39 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1619,33 +1615,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 714,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1662,12 +1658,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1739,14 +1735,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1769,7 +1765,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 714,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1778,24 +1774,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>15</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1812,12 +1808,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1889,14 +1885,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1922,17 +1918,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1962,12 +1958,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2039,14 +2035,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2069,33 +2065,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 584,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>7</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2112,12 +2108,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2189,14 +2185,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2219,7 +2215,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 584,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2228,24 +2224,24 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,5%</t>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2262,12 +2258,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2339,14 +2335,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2378,11 +2374,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 45,5%</t>
+        <v>14</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2412,12 +2408,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2489,14 +2485,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2522,17 +2518,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,5%</t>
+          <t>▲ 45,5%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2562,12 +2558,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2639,14 +2635,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2669,33 +2665,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+        <v>11</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2712,12 +2708,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2789,14 +2785,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2819,7 +2815,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2828,24 +2824,24 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,2%</t>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2862,12 +2858,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2939,14 +2935,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2978,11 +2974,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 83,3%</t>
+        <v>9</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,2%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3012,12 +3008,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3089,14 +3085,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3128,11 +3124,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>11</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3162,12 +3158,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3239,14 +3235,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3272,17 +3268,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3312,12 +3308,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3389,14 +3385,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3419,33 +3415,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>9</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3462,12 +3458,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3539,14 +3535,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3569,7 +3565,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3580,22 +3576,22 @@
       <c r="I42" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3612,12 +3608,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3689,14 +3685,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3722,17 +3718,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3762,12 +3758,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3839,14 +3835,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3869,33 +3865,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="M46" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3912,12 +3908,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3989,14 +3985,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4019,7 +4015,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4041,11 +4037,11 @@
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4062,12 +4058,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4139,12 +4135,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4180,9 +4176,9 @@
       <c r="I50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4212,12 +4208,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4289,14 +4285,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4328,11 +4324,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4362,12 +4358,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4439,14 +4435,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4478,11 +4474,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4512,12 +4508,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4589,14 +4585,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4622,17 +4618,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,7%</t>
+        <v>12</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4662,12 +4658,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4739,14 +4735,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4769,33 +4765,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 175,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 114,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4812,12 +4808,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4889,14 +4885,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4919,33 +4915,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 175,00</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>15</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4962,12 +4958,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5039,14 +5035,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5069,33 +5065,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5112,14 +5108,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5142,7 +5138,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5150,8 +5146,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>0</v>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5160,39 +5158,41 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5220,20 +5220,20 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,1%</t>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5299,9 +5299,9 @@
       <c r="I65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5331,14 +5331,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5370,24 +5370,24 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 35,7%</t>
+        <v>15</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5404,14 +5404,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5443,11 +5443,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5477,14 +5477,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5510,17 +5510,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,7%</t>
+        <v>19</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5550,14 +5550,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5588,10 +5588,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I69" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5600,41 +5598,39 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5657,33 +5653,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5700,12 +5696,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5777,14 +5773,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5807,7 +5803,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 55,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5816,24 +5812,24 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>15</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5850,12 +5846,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5927,14 +5923,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5966,11 +5962,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 250,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6000,12 +5996,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6077,14 +6073,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6110,17 +6106,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6150,12 +6146,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6227,14 +6223,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6257,33 +6253,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6300,12 +6296,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6377,14 +6373,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6407,33 +6403,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6450,12 +6446,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6527,14 +6523,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6557,33 +6553,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6600,82 +6596,232 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>UTD-027-BR</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Porta Talheres Extensivel Branco</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>6421065554</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O83" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O83"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 38,5%</t>
+          <t>▼ 54,5%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,8 +670,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -680,37 +682,39 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +739,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 163,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+        <v>33</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,1%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +812,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -816,47 +820,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,12 +889,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
+          <t>R$ 111,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
@@ -894,7 +902,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▲ 10,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -907,7 +915,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,7 +962,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -962,8 +970,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n">
-        <v>1</v>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -972,37 +982,39 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1039,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 81,2%</t>
+        <v>16</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 38,5%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,7 +1112,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1108,10 +1120,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1120,39 +1130,37 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1177,33 +1185,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,0%</t>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1220,12 +1228,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1261,9 +1269,9 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1293,12 +1301,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1323,33 +1331,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 264,00</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,5%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▲ 8,7%</t>
+          <t>▲ 10,3%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1366,12 +1374,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1405,7 +1413,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1439,12 +1447,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1469,33 +1477,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 212,00</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▲ 53,3%</t>
+          <t>▲ 81,2%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1512,12 +1520,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1542,7 +1550,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1550,8 +1558,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1560,37 +1570,39 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1615,33 +1627,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>▼ 85,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>16</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1658,12 +1670,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1688,7 +1700,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1696,10 +1708,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1708,39 +1718,37 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1765,25 +1773,25 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 714,00</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 264,00</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▲ 8,7%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
@@ -1791,7 +1799,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1808,12 +1816,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1838,7 +1846,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1846,10 +1854,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1858,39 +1864,37 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1915,33 +1919,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 212,00</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>23</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 53,3%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1958,12 +1962,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1988,7 +1992,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1996,10 +2000,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2008,39 +2010,37 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2065,33 +2065,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 106,00</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 85,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>15</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2108,12 +2108,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 584,00</t>
+          <t>R$ 714,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2224,24 +2224,24 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>15</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2374,11 +2374,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,5%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2518,17 +2518,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>▲ 45,5%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2558,12 +2558,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2665,33 +2665,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 584,00</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2708,12 +2708,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2785,12 +2785,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2824,24 +2824,24 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,1%</t>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2974,11 +2974,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,2%</t>
+        <v>16</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 45,5%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3008,12 +3008,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3085,12 +3085,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3118,9 +3118,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▲ 83,3%</t>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3274,24 +3274,24 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3385,12 +3385,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3418,17 +3418,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,5%</t>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,2%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3458,12 +3458,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3574,24 +3574,24 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>11</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3685,12 +3685,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3724,11 +3724,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3874,11 +3874,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3985,12 +3985,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4024,16 +4024,16 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
@@ -4058,12 +4058,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4174,11 +4174,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4318,17 +4318,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4358,12 +4358,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4474,11 +4474,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4487,11 +4487,11 @@
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4585,12 +4585,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4624,11 +4624,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4658,12 +4658,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4735,12 +4735,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4768,17 +4768,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4885,12 +4885,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 175,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4924,24 +4924,24 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 114,3%</t>
+        <v>9</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4958,12 +4958,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5035,12 +5035,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5068,17 +5068,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5215,33 +5215,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>▼ 53,3%</t>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5296,8 +5296,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5306,37 +5308,39 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5361,7 +5365,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 175,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5372,22 +5376,22 @@
       <c r="I66" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,1%</t>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5404,12 +5408,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5434,7 +5438,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5442,47 +5446,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5510,17 +5518,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 35,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5550,12 +5558,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5580,7 +5588,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5588,8 +5596,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>1</v>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5598,37 +5608,39 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5653,33 +5665,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,7%</t>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5696,12 +5708,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5726,7 +5738,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5734,10 +5746,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5746,39 +5756,37 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5803,7 +5811,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5814,9 +5822,9 @@
       <c r="I72" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5829,7 +5837,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5846,12 +5854,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5876,7 +5884,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5884,51 +5892,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5962,11 +5966,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>19</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5996,12 +6000,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6026,7 +6030,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6034,10 +6038,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I75" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6046,39 +6048,37 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6106,17 +6106,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 250,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6253,33 +6253,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6412,24 +6412,24 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6446,12 +6446,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6556,17 +6556,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+        <v>7</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6703,33 +6703,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6746,82 +6746,532 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>UTD-027-BR</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Porta Talheres Extensivel Branco</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>6421065554</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 409,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 40,1%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 54,5%</t>
+        <v>73</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -744,28 +744,28 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>▲ 163,1%</t>
+          <t>▼ 16,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 111,00</t>
+          <t>R$ 350,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -898,24 +898,24 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>53</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 253,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 38,5%</t>
+        <v>15</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▼ 54,5%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1120,8 +1120,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1130,37 +1132,39 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1185,33 +1189,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▲ 163,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,8%</t>
+          <t>▲ 3,1%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1228,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1258,7 +1262,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1266,47 +1270,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1331,20 +1339,20 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
+          <t>R$ 111,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,3%</t>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1357,7 +1365,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1374,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1404,7 +1412,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1412,8 +1420,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
-        <v>1</v>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1422,37 +1432,39 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1477,33 +1489,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▲ 81,2%</t>
+          <t>▼ 38,5%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1520,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1550,7 +1562,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1558,10 +1570,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1570,39 +1580,37 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1627,33 +1635,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1670,12 +1678,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1711,9 +1719,9 @@
       <c r="I17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1743,12 +1751,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1773,33 +1781,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 264,00</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,5%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,7%</t>
+        <v>32</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▲ 10,3%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1816,12 +1824,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1855,7 +1863,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1889,12 +1897,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1919,33 +1927,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 212,00</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 53,3%</t>
+        <v>29</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 81,2%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1962,12 +1970,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1992,7 +2000,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2000,8 +2008,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2010,37 +2020,39 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2065,33 +2077,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 85,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>16</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▼ 36,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2108,12 +2120,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2138,7 +2150,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2146,10 +2158,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2158,39 +2168,37 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2215,25 +2223,25 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 714,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 264,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▲ 24,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▲ 8,7%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
@@ -2241,7 +2249,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2258,12 +2266,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2288,7 +2296,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2296,10 +2304,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2308,39 +2314,37 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2365,33 +2369,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 212,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 53,3%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2408,12 +2412,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2438,7 +2442,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2446,10 +2450,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2458,39 +2460,37 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2515,33 +2515,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>▼ 85,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>15</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2558,12 +2558,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 584,00</t>
+          <t>R$ 714,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2674,24 +2674,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,1%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2708,12 +2708,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2785,12 +2785,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2824,11 +2824,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2968,17 +2968,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 45,5%</t>
+        <v>7</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3008,12 +3008,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3085,12 +3085,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3115,33 +3115,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 584,00</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,5%</t>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3274,24 +3274,24 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+        <v>14</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3385,12 +3385,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3424,11 +3424,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,2%</t>
+          <t>▲ 45,5%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3458,12 +3458,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3568,17 +3568,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 83,3%</t>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3685,12 +3685,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3724,24 +3724,24 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3868,9 +3868,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,5%</t>
+          <t>▼ 18,2%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3985,12 +3985,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4024,24 +4024,24 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>11</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4174,11 +4174,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4318,17 +4318,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4358,12 +4358,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4474,16 +4474,16 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
@@ -4508,12 +4508,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4585,12 +4585,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4624,11 +4624,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4658,12 +4658,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4735,12 +4735,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4768,17 +4768,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4885,12 +4885,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4924,11 +4924,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4937,11 +4937,11 @@
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4958,12 +4958,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5035,12 +5035,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5074,11 +5074,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5218,17 +5218,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 175,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5374,24 +5374,24 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▲ 114,3%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5485,12 +5485,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5518,17 +5518,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5635,12 +5635,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5665,33 +5665,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5746,8 +5746,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
-        <v>0</v>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5756,37 +5758,39 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5811,7 +5815,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 175,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5824,20 +5828,20 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,1%</t>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5854,12 +5858,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5884,7 +5888,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5892,47 +5896,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5960,17 +5968,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 35,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6000,12 +6008,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6030,7 +6038,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6038,8 +6046,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>1</v>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6048,37 +6058,39 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6103,33 +6115,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6146,12 +6158,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6176,7 +6188,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6184,10 +6196,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6196,39 +6206,37 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6253,7 +6261,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6266,7 +6274,7 @@
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6279,7 +6287,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6296,12 +6304,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6326,7 +6334,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6334,51 +6342,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6412,11 +6416,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6446,12 +6450,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6476,7 +6480,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6484,10 +6488,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I81" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6496,39 +6498,37 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6556,17 +6556,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>▲ 250,0%</t>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6703,33 +6703,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6746,12 +6746,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6823,12 +6823,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6862,24 +6862,24 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6896,12 +6896,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6973,12 +6973,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7006,17 +7006,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▼ 37,5%</t>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7123,12 +7123,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7153,33 +7153,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7196,82 +7196,532 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>UTD-027-BR</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Porta Talheres Extensivel Branco</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>6421065554</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O91" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O91"/>
+  <autoFilter ref="A1:O97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 409,00</t>
+          <t>R$ 117,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▲ 40,1%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>67</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,2%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,14 +709,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -739,33 +739,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
+          <t>R$ 409,00</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,6%</t>
+          <t>▲ 40,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>73</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +859,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -889,33 +889,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 350,00</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▲ 253,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,14 +1009,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1039,33 +1039,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 350,00</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>▼ 54,5%</t>
+          <t>▲ 253,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,14 +1159,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1189,33 +1189,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>▲ 163,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▲ 3,1%</t>
+          <t>▼ 54,5%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,14 +1309,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1339,33 +1339,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 111,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 163,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>33</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,1%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,14 +1459,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1489,33 +1489,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 111,00</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▼ 38,5%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1532,14 +1532,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1570,8 +1570,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1580,39 +1582,41 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1635,33 +1639,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+        <v>16</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 38,5%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1678,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1719,9 +1723,9 @@
       <c r="I17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1751,14 +1755,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1790,24 +1794,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▲ 10,3%</t>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1824,14 +1828,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1863,11 +1867,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1897,14 +1901,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1932,20 +1936,20 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▲ 81,2%</t>
+        <v>32</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,3%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
@@ -1953,7 +1957,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1970,14 +1974,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2000,7 +2004,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2008,10 +2012,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I21" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2020,41 +2022,39 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2077,33 +2077,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>▼ 36,0%</t>
+          <t>▲ 81,2%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2120,14 +2120,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2158,8 +2158,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2168,39 +2170,41 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2223,33 +2227,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 264,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>▲ 24,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▲ 8,7%</t>
+          <t>▼ 36,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2266,12 +2270,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2339,14 +2343,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2369,25 +2373,25 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 212,00</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 264,00</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▲ 53,3%</t>
+        <v>25</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,7%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
@@ -2395,7 +2399,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2412,12 +2416,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2485,14 +2489,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2515,33 +2519,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
+          <t>R$ 212,00</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>▼ 85,2%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>23</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 53,3%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2558,14 +2562,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2588,7 +2592,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2596,10 +2600,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2608,41 +2610,39 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2665,33 +2665,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 714,00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,2%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2708,12 +2708,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2785,14 +2785,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 714,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2824,24 +2824,24 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2935,14 +2935,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2968,17 +2968,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3008,12 +3008,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3085,14 +3085,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3115,33 +3115,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 584,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▼ 57,1%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3235,14 +3235,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 584,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3274,24 +3274,24 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▼ 12,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3385,14 +3385,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3424,11 +3424,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▲ 45,5%</t>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3458,12 +3458,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3535,14 +3535,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3568,17 +3568,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>16</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 45,5%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3685,14 +3685,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3715,33 +3715,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>▼ 11,1%</t>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3835,14 +3835,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3874,24 +3874,24 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,2%</t>
+        <v>8</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3985,14 +3985,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4024,11 +4024,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▲ 83,3%</t>
+          <t>▼ 18,2%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4135,14 +4135,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4174,11 +4174,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4285,14 +4285,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4318,17 +4318,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▲ 12,5%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4358,12 +4358,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4435,14 +4435,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4465,33 +4465,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>9</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4585,14 +4585,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4615,7 +4615,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4626,22 +4626,22 @@
       <c r="I56" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4658,12 +4658,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4735,14 +4735,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4768,17 +4768,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4885,14 +4885,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4915,33 +4915,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="M60" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4958,12 +4958,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5035,14 +5035,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5065,7 +5065,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5087,11 +5087,11 @@
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5226,9 +5226,9 @@
       <c r="I64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5335,14 +5335,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5374,11 +5374,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5485,14 +5485,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5524,11 +5524,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5635,14 +5635,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5668,17 +5668,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▼ 46,7%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5785,14 +5785,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5815,33 +5815,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 175,00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▲ 114,3%</t>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5935,14 +5935,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5965,33 +5965,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 175,00</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>15</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6085,14 +6085,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6115,33 +6115,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6158,14 +6158,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6196,8 +6196,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>0</v>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6206,39 +6208,41 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6266,20 +6270,20 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▼ 21,1%</t>
+        <v>7</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
@@ -6287,7 +6291,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6304,12 +6308,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6345,9 +6349,9 @@
       <c r="I79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6377,14 +6381,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6407,7 +6411,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6416,24 +6420,24 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▲ 35,7%</t>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6450,14 +6454,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6489,11 +6493,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6523,14 +6527,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6556,17 +6560,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,7%</t>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6596,14 +6600,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6626,7 +6630,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6634,10 +6638,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I83" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6646,41 +6648,39 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6703,33 +6703,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6746,12 +6746,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6823,14 +6823,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 55,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6862,24 +6862,24 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6896,12 +6896,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6973,14 +6973,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7012,11 +7012,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▲ 250,0%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7123,14 +7123,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7156,17 +7156,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H90" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7273,14 +7273,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7303,33 +7303,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7423,14 +7423,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7453,33 +7453,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7573,14 +7573,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7603,33 +7603,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7646,82 +7646,232 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>UTD-027-BR</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Porta Talheres Extensivel Branco</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>6421065554</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O97" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O97"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 117,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▼ 85,8%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,2%</t>
+        <v>54</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,9%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,10 +670,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -682,39 +680,37 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -744,28 +740,28 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>▲ 40,1%</t>
+          <t>▲ 249,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>47</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 29,9%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +855,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -889,33 +885,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
+          <t>R$ 117,00</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,6%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 8,2%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +928,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1005,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1039,25 +1035,25 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 350,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 409,00</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 253,3%</t>
+        <v>73</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
@@ -1065,7 +1061,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,12 +1078,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1155,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1189,33 +1185,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 292,00</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
+          <t>▼ 16,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 54,5%</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1232,12 +1228,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,12 +1305,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1339,33 +1335,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 163,1%</t>
+          <t>R$ 350,00</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,1%</t>
+          <t>▲ 253,3%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1382,12 +1378,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,12 +1455,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1489,33 +1485,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 111,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 54,5%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1532,12 +1528,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,12 +1605,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1639,33 +1635,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 163,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 38,5%</t>
+        <v>33</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,1%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1682,12 +1678,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1712,7 +1708,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1720,8 +1716,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1730,37 +1728,39 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1785,33 +1785,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
+          <t>R$ 111,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+        <v>32</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1866,47 +1866,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1931,33 +1935,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,3%</t>
+        <v>16</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 38,5%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1974,12 +1978,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2013,7 +2017,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2047,12 +2051,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2082,28 +2086,28 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 81,2%</t>
+        <v>26</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2120,12 +2124,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2150,7 +2154,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2158,51 +2162,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2227,33 +2227,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,0%</t>
+        <v>32</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,3%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2270,12 +2270,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2343,12 +2343,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2373,33 +2373,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 264,00</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,5%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▲ 8,7%</t>
+          <t>▲ 81,2%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2416,12 +2416,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2454,8 +2454,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2464,37 +2466,39 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2519,33 +2523,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 212,00</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 53,3%</t>
+        <v>16</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2562,12 +2566,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2635,12 +2639,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2665,33 +2669,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 85,2%</t>
+          <t>R$ 264,00</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>25</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,7%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2708,12 +2712,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2738,7 +2742,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2746,10 +2750,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2758,39 +2760,37 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2815,25 +2815,25 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 714,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 212,00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▲ 53,3%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2896,10 +2896,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2908,39 +2906,37 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2965,33 +2961,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,2%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>15</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3008,12 +3004,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3085,12 +3081,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3115,33 +3111,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 714,00</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3158,12 +3154,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3235,12 +3231,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3265,7 +3261,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 584,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3278,20 +3274,20 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,1%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3308,12 +3304,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3385,12 +3381,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3418,17 +3414,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,5%</t>
+        <v>7</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3458,12 +3454,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3535,12 +3531,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3565,7 +3561,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 584,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3574,24 +3570,24 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 45,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3608,12 +3604,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3685,12 +3681,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3718,17 +3714,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>14</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3758,12 +3754,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3835,12 +3831,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3865,7 +3861,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3874,24 +3870,24 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+        <v>16</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 45,5%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3908,12 +3904,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3985,12 +3981,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4018,17 +4014,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,2%</t>
+        <v>11</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4058,12 +4054,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4135,12 +4131,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4165,7 +4161,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4174,24 +4170,24 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 83,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4208,12 +4204,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4285,12 +4281,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4324,11 +4320,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 18,2%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4358,12 +4354,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4435,12 +4431,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4468,17 +4464,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,5%</t>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4508,12 +4504,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4585,12 +4581,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4615,7 +4611,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4624,24 +4620,24 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4658,12 +4654,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4735,12 +4731,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4768,17 +4764,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4808,12 +4804,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4885,12 +4881,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4915,33 +4911,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4958,12 +4954,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5035,12 +5031,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5065,7 +5061,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5074,24 +5070,24 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="M62" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5108,12 +5104,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5185,12 +5181,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5218,13 +5214,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5258,12 +5254,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5335,12 +5331,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5365,7 +5361,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5376,9 +5372,9 @@
       <c r="I66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5387,11 +5383,11 @@
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5408,12 +5404,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5485,12 +5481,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5524,11 +5520,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5558,12 +5554,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5635,12 +5631,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5674,11 +5670,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5708,12 +5704,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5785,12 +5781,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5818,17 +5814,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▼ 46,7%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5858,12 +5854,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5935,12 +5931,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5965,7 +5961,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 175,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5974,24 +5970,24 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▲ 114,3%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6008,12 +6004,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6085,12 +6081,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6124,11 +6120,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>8</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6158,12 +6154,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6235,12 +6231,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6265,33 +6261,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 175,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+        <v>15</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6308,12 +6304,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6338,7 +6334,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6346,8 +6342,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="n">
-        <v>0</v>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6356,37 +6354,39 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6411,33 +6411,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,1%</t>
+        <v>7</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6492,47 +6492,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6557,33 +6561,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 35,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6600,12 +6604,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6639,7 +6643,7 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6673,12 +6677,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6703,33 +6707,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,7%</t>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6746,12 +6750,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6776,7 +6780,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6784,51 +6788,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6862,24 +6862,24 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6896,12 +6896,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6934,10 +6934,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I87" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6946,39 +6944,37 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7006,17 +7002,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7046,12 +7042,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7123,12 +7119,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7153,7 +7149,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 55,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7162,24 +7158,24 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>▲ 250,0%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7196,12 +7192,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7273,12 +7269,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7306,17 +7302,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7346,12 +7342,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7423,12 +7419,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7453,7 +7449,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7462,24 +7458,24 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7496,12 +7492,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7573,12 +7569,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7612,11 +7608,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>▼ 37,5%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7646,12 +7642,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7723,12 +7719,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7762,16 +7758,16 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
@@ -7779,7 +7775,7 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7796,82 +7792,382 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>UTD-027-BR</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Porta Talheres Extensivel Branco</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>6421065554</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O99" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:O103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▼ 85,8%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,9%</t>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,8 +670,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -680,37 +682,39 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +739,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 409,00</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 249,6%</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 29,9%</t>
+        <v>11</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -855,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -888,30 +892,30 @@
           <t>R$ 117,00</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,2%</t>
+        <v>9</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -928,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1005,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1035,33 +1039,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 409,00</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1078,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1155,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1185,33 +1189,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1228,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1305,12 +1309,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1335,33 +1339,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 350,00</t>
+          <t>R$ 117,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 253,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 74,2%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1378,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1455,12 +1459,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1485,33 +1489,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 117,00</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 54,5%</t>
+        <v>31</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 47,6%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1528,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1605,12 +1609,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1638,30 +1642,30 @@
           <t>R$ 292,00</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 163,1%</t>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,1%</t>
+        <v>21</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1678,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1755,12 +1759,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1785,7 +1789,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 111,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1794,24 +1798,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 30,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1828,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1905,12 +1909,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1938,17 +1942,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 38,5%</t>
+        <v>30</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1978,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2008,7 +2012,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2016,8 +2020,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2026,37 +2032,39 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2081,33 +2089,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,8%</t>
+          <t>▼ 6,2%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2124,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2154,7 +2162,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2162,47 +2170,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2227,7 +2239,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2236,11 +2248,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,3%</t>
+        <v>16</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 70,4%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2249,11 +2261,11 @@
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2270,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2309,7 +2321,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2343,12 +2355,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2373,33 +2385,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▲ 81,2%</t>
+          <t>▲ 14,9%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2416,12 +2428,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2446,7 +2458,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2454,10 +2466,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2466,39 +2476,37 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2523,33 +2531,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 409,00</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 249,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,0%</t>
+          <t>▼ 29,9%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2566,12 +2574,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2596,7 +2604,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2604,8 +2612,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2614,37 +2624,39 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2669,33 +2681,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 264,00</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,5%</t>
+          <t>R$ 117,00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,7%</t>
+        <v>67</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,2%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2712,12 +2724,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2742,7 +2754,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2750,8 +2762,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2760,37 +2774,39 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2815,33 +2831,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 212,00</t>
+          <t>R$ 409,00</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 40,1%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 53,3%</t>
+        <v>73</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2858,12 +2874,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2888,7 +2904,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2896,8 +2912,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n">
-        <v>0</v>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2906,37 +2924,39 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2961,33 +2981,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
+          <t>R$ 292,00</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>▼ 85,2%</t>
+          <t>▼ 16,6%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3004,12 +3024,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3081,12 +3101,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3111,7 +3131,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 714,00</t>
+          <t>R$ 350,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3120,24 +3140,24 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▲ 253,3%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3154,12 +3174,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3231,12 +3251,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3264,17 +3284,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 54,5%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3304,12 +3324,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3381,12 +3401,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3411,33 +3431,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 163,1%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▲ 3,1%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3454,12 +3474,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3531,12 +3551,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3561,7 +3581,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 584,00</t>
+          <t>R$ 111,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3570,24 +3590,24 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>32</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3604,12 +3624,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3681,12 +3701,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3714,17 +3734,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,5%</t>
+          <t>▼ 38,5%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3754,12 +3774,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3784,7 +3804,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3792,10 +3812,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3804,39 +3822,37 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3861,33 +3877,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 106,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 45,5%</t>
+        <v>26</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3904,12 +3920,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3934,7 +3950,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3942,51 +3958,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4011,33 +4023,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,5%</t>
+          <t>▲ 10,3%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4054,12 +4066,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4084,7 +4096,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4092,10 +4104,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I49" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4104,39 +4114,37 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4161,7 +4169,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 106,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4170,24 +4178,24 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+        <v>29</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 81,2%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4204,12 +4212,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4281,12 +4289,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4314,17 +4322,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,2%</t>
+          <t>▼ 36,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4354,12 +4362,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4384,7 +4392,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4392,10 +4400,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4404,39 +4410,37 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4461,33 +4465,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 264,00</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,5%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>▲ 83,3%</t>
+          <t>▲ 8,7%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4504,12 +4508,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4534,7 +4538,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4542,10 +4546,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4554,39 +4556,37 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4611,33 +4611,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 212,00</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>23</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 53,3%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4692,10 +4692,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4704,39 +4702,37 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4761,33 +4757,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 106,00</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 85,2%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,5%</t>
+        <v>15</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4804,12 +4800,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4881,12 +4877,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4911,7 +4907,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 714,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4920,24 +4916,24 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>15</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4954,12 +4950,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5031,12 +5027,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5070,11 +5066,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5104,12 +5100,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5181,12 +5177,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5220,11 +5216,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5254,12 +5250,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5331,12 +5327,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5361,7 +5357,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 584,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5370,16 +5366,16 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
@@ -5387,7 +5383,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5404,12 +5400,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5481,12 +5477,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5520,11 +5516,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5554,12 +5550,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5631,12 +5627,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5670,11 +5666,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 45,5%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5704,12 +5700,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5781,12 +5777,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5814,17 +5810,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5854,12 +5850,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5931,12 +5927,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5961,7 +5957,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5970,24 +5966,24 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6004,12 +6000,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6081,12 +6077,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6114,17 +6110,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 46,7%</t>
+          <t>▼ 18,2%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6154,12 +6150,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6231,12 +6227,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6261,7 +6257,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 175,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6270,24 +6266,24 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▲ 114,3%</t>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6304,12 +6300,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6381,12 +6377,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6414,17 +6410,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6454,12 +6450,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6531,12 +6527,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6561,33 +6557,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+        <v>9</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6604,12 +6600,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6634,7 +6630,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6642,8 +6638,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
-        <v>0</v>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6652,37 +6650,39 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6716,16 +6716,16 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,1%</t>
+        <v>8</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6788,47 +6788,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6862,11 +6866,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>▲ 35,7%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6896,12 +6900,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6926,7 +6930,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6934,8 +6938,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="n">
-        <v>1</v>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6944,37 +6950,39 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7008,11 +7016,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7042,12 +7050,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7119,12 +7127,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7149,7 +7157,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7158,16 +7166,16 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
@@ -7175,7 +7183,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7192,12 +7200,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7269,12 +7277,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7308,11 +7316,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7342,12 +7350,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7419,12 +7427,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7458,11 +7466,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 250,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7492,12 +7500,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7569,12 +7577,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7602,17 +7610,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7642,12 +7650,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7719,12 +7727,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7749,7 +7757,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -7758,24 +7766,24 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7792,12 +7800,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7869,12 +7877,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7908,11 +7916,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>▼ 37,5%</t>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7942,12 +7950,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8019,12 +8027,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8049,7 +8057,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 175,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -8058,24 +8066,24 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>15</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8092,82 +8100,1870 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,1%</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 35,7%</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 250,0%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>UTD-027-BR</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Porta Talheres Extensivel Branco</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>6421065554</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O103" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
+  <autoFilter ref="A1:O127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 117,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>▲ 18,2%</t>
+        <v>67</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,1%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -739,33 +739,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,4%</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>11</v>
+        <v>86</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▲ 22,2%</t>
+          <t>▲ 22,9%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -889,33 +889,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 117,00</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 234,00</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 303,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▲ 350,0%</t>
+          <t>▲ 12,9%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1039,33 +1039,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>62</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,1%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1120,10 +1120,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1132,39 +1130,37 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1189,33 +1185,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 234,00</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 19,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>73</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 19,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1232,12 +1228,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1262,7 +1258,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1270,51 +1266,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1339,33 +1331,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 117,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 149,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▼ 74,2%</t>
+          <t>▼ 16,4%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1382,12 +1374,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1412,7 +1404,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1420,10 +1412,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I13" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1432,39 +1422,37 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1494,20 +1482,20 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>▼ 59,9%</t>
+          <t>▼ 66,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 47,6%</t>
+        <v>73</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
@@ -1515,7 +1503,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1532,12 +1520,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,12 +1597,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1639,33 +1627,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 350,00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 46,2%</t>
+          <t>▼ 8,9%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1682,12 +1670,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,12 +1747,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1789,33 +1777,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 234,00</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▲ 30,0%</t>
+          <t>▲ 34,3%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1832,12 +1820,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,12 +1897,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1939,33 +1927,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 175,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 42,6%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1982,12 +1970,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,12 +2047,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2089,33 +2077,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 175,00</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 25,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,2%</t>
+        <v>47</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,9%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2132,12 +2120,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,12 +2197,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2239,33 +2227,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 234,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 70,4%</t>
+        <v>42</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 27,3%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2282,12 +2270,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2312,7 +2300,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2320,8 +2308,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2330,37 +2320,39 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2385,33 +2377,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 85,8%</t>
+          <t>R$ 409,00</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 133,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,9%</t>
+          <t>▲ 6,5%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2428,12 +2420,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2458,7 +2450,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2466,8 +2458,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2476,37 +2470,39 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2531,33 +2527,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 409,00</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 249,6%</t>
+          <t>R$ 175,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 29,9%</t>
+        <v>31</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 72,2%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2574,12 +2570,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2651,12 +2647,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2681,33 +2677,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 117,00</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,8%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,2%</t>
+        <v>18</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2724,12 +2720,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2801,12 +2797,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2831,33 +2827,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 409,00</t>
+          <t>R$ 234,00</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>▲ 40,1%</t>
+          <t>▲ 33,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>18</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 38,5%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2874,12 +2870,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2951,12 +2947,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2981,33 +2977,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,6%</t>
+          <t>R$ 175,00</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 201,7%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3024,12 +3020,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3101,12 +3097,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3131,33 +3127,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 350,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▲ 253,3%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3174,12 +3170,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3251,12 +3247,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3281,33 +3277,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▼ 54,5%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3324,12 +3320,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3401,12 +3397,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3431,33 +3427,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 163,1%</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,1%</t>
+        <v>5</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3474,12 +3470,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3551,12 +3547,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3581,7 +3577,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 111,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3590,24 +3586,24 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3624,12 +3620,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3701,12 +3697,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3740,11 +3736,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 38,5%</t>
+        <v>13</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3774,12 +3770,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3804,7 +3800,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3812,8 +3808,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
-        <v>0</v>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3822,37 +3820,39 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3877,25 +3877,25 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,4%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+        <v>11</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3920,12 +3920,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3958,47 +3958,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4023,33 +4027,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
+          <t>R$ 117,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>▲ 10,3%</t>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4066,12 +4070,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4096,7 +4100,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4104,8 +4108,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>1</v>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4114,37 +4120,39 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4169,7 +4177,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4178,24 +4186,24 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>▲ 81,2%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4212,12 +4220,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4289,12 +4297,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4328,11 +4336,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,0%</t>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4362,12 +4370,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4392,7 +4400,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4400,8 +4408,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4410,37 +4420,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4465,33 +4477,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 264,00</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,5%</t>
+          <t>R$ 117,00</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,7%</t>
+        <v>8</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 74,2%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4508,12 +4520,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4538,7 +4550,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4546,8 +4558,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4556,37 +4570,39 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4611,33 +4627,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 212,00</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 117,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▲ 53,3%</t>
+          <t>▲ 47,6%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4654,12 +4670,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4684,7 +4700,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4692,8 +4708,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>0</v>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4702,37 +4720,39 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4757,33 +4777,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 85,2%</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>21</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4800,12 +4820,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4877,12 +4897,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4907,7 +4927,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 714,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4916,24 +4936,24 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▲ 30,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4950,12 +4970,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5027,12 +5047,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5066,11 +5086,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>30</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5100,12 +5120,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5177,12 +5197,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5216,11 +5236,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>15</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,2%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5250,12 +5270,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5327,12 +5347,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5357,25 +5377,25 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 584,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,1%</t>
+          <t>▼ 70,4%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
@@ -5383,7 +5403,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5400,12 +5420,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5430,7 +5450,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5438,10 +5458,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5450,39 +5468,37 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5507,33 +5523,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,8%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,5%</t>
+        <v>54</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,9%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5550,12 +5566,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5580,7 +5596,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5588,10 +5604,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5600,39 +5614,37 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5657,33 +5669,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 409,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 249,6%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 45,5%</t>
+        <v>47</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 29,9%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5700,12 +5712,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5777,12 +5789,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5807,33 +5819,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 117,00</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>67</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,2%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5850,12 +5862,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5927,12 +5939,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5957,33 +5969,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 409,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,1%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+        <v>73</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6000,12 +6012,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6077,12 +6089,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6107,20 +6119,20 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,6%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6129,11 +6141,11 @@
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6150,12 +6162,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6227,12 +6239,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6257,7 +6269,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 350,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6266,24 +6278,24 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▲ 83,3%</t>
+          <t>▲ 253,3%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6300,12 +6312,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6377,12 +6389,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6410,17 +6422,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 54,5%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6450,12 +6462,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6527,12 +6539,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6557,33 +6569,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 163,1%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,5%</t>
+          <t>▲ 3,1%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6600,12 +6612,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6677,12 +6689,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6707,7 +6719,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 111,00</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6716,24 +6728,24 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>32</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6750,12 +6762,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6827,12 +6839,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6860,17 +6872,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>16</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 38,5%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6900,12 +6912,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6930,7 +6942,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6938,10 +6950,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I87" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6950,39 +6960,37 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7007,33 +7015,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>26</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7050,12 +7058,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7080,7 +7088,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7088,51 +7096,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7157,33 +7161,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 106,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>32</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,3%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7200,12 +7204,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7230,7 +7234,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7238,10 +7242,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I91" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7250,39 +7252,37 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 106,00</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7316,24 +7316,24 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>29</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 81,2%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7350,12 +7350,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7460,17 +7460,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 36,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7538,10 +7538,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I95" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7550,39 +7548,37 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7607,33 +7603,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 264,00</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,5%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,7%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7650,12 +7646,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7680,7 +7676,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7688,10 +7684,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -7700,39 +7694,37 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7757,33 +7749,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 212,00</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 53,3%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7800,12 +7792,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7830,7 +7822,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7838,10 +7830,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I99" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -7850,39 +7840,37 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7907,33 +7895,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 106,00</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 85,2%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,7%</t>
+        <v>15</v>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7950,12 +7938,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8027,12 +8015,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8057,7 +8045,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 175,00</t>
+          <t>R$ 714,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -8070,20 +8058,20 @@
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>▲ 114,3%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8100,12 +8088,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8177,12 +8165,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8210,17 +8198,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8250,12 +8238,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8327,12 +8315,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8357,33 +8345,33 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8400,12 +8388,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8430,7 +8418,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -8438,8 +8426,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I107" s="2" t="n">
-        <v>0</v>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
@@ -8448,37 +8438,39 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8503,7 +8495,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 584,00</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -8512,16 +8504,16 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,1%</t>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
@@ -8529,7 +8521,7 @@
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8546,12 +8538,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8576,7 +8568,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -8584,47 +8576,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8658,11 +8654,11 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>▲ 35,7%</t>
+        <v>14</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8692,12 +8688,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8722,7 +8718,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -8730,8 +8726,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I111" s="2" t="n">
-        <v>1</v>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
@@ -8740,37 +8738,39 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8798,17 +8798,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,7%</t>
+        <v>16</v>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 45,5%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8915,12 +8915,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8945,33 +8945,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9065,12 +9065,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -9104,24 +9104,24 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9254,11 +9254,11 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>▲ 250,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,2%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9288,12 +9288,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9365,12 +9365,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9398,17 +9398,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9438,12 +9438,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9515,12 +9515,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -9554,24 +9554,24 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9588,12 +9588,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9665,12 +9665,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9704,11 +9704,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+        <v>9</v>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9888,82 +9888,3220 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,7%</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 175,00</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>▲ 114,3%</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>13,3%</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,1%</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>▲ 35,7%</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>▲ 250,0%</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>UTD-027-BR</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>Porta Talheres Extensivel Branco</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>6421065554</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O127"/>
+  <autoFilter ref="A1:O169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
@@ -657,7 +657,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -10663,7 +10663,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -10963,7 +10963,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -11263,7 +11263,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -11563,7 +11563,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -11709,7 +11709,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -11855,7 +11855,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -12601,7 +12601,7 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -12751,7 +12751,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
@@ -13051,7 +13051,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 64,90</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">

--- a/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 117,00</t>
+          <t>R$ 350,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▼ 59,9%</t>
+          <t>▲ 199,1%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,1%</t>
+        <v>59</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,9%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,14 +709,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -739,33 +739,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
+          <t>R$ 117,00</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>▲ 24,8%</t>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▲ 22,9%</t>
+          <t>▼ 22,1%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +859,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -889,25 +889,25 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 303,4%</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 24,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,9%</t>
+        <v>86</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,9%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
@@ -915,7 +915,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,14 +1009,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1039,33 +1039,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 234,00</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,2%</t>
+          <t>▲ 303,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,1%</t>
+          <t>▲ 12,9%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,14 +1082,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1120,8 +1120,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1130,39 +1132,41 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1185,33 +1189,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 19,9%</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>▲ 19,7%</t>
+          <t>▼ 15,1%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1228,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1269,9 +1273,9 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1301,14 +1305,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1331,29 +1335,29 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
+          <t>R$ 234,00</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>▲ 149,6%</t>
+          <t>▼ 19,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,4%</t>
+          <t>▲ 19,7%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
@@ -1374,14 +1378,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1413,11 +1417,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1447,14 +1451,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1477,33 +1481,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 117,00</t>
+          <t>R$ 292,00</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,6%</t>
+          <t>▲ 149,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,0%</t>
+        <v>61</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,4%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1520,14 +1524,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1550,7 +1554,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1558,10 +1562,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I15" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1570,41 +1572,39 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1627,33 +1627,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 350,00</t>
+          <t>R$ 117,00</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>▲ 49,6%</t>
+          <t>▼ 66,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,9%</t>
+        <v>73</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1747,14 +1747,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1777,33 +1777,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,7%</t>
+          <t>R$ 350,00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▲ 49,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▲ 34,3%</t>
+          <t>▼ 8,9%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1820,12 +1820,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1897,14 +1897,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1927,33 +1927,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 175,00</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 234,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 42,6%</t>
+        <v>90</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 34,3%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1970,12 +1970,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2047,14 +2047,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2080,22 +2080,22 @@
           <t>R$ 175,00</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,2%</t>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,9%</t>
+        <v>67</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▲ 42,6%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2197,14 +2197,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2227,33 +2227,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,8%</t>
+          <t>R$ 175,00</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 27,3%</t>
+        <v>47</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▲ 11,9%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2270,12 +2270,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2347,14 +2347,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2377,33 +2377,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 409,00</t>
+          <t>R$ 234,00</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>▲ 133,7%</t>
+          <t>▼ 42,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,5%</t>
+        <v>42</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▲ 27,3%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2497,14 +2497,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2527,33 +2527,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 175,00</t>
+          <t>R$ 409,00</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,1%</t>
+          <t>▲ 133,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 72,2%</t>
+        <v>33</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▲ 6,5%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2570,12 +2570,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2647,14 +2647,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2677,33 +2677,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
+          <t>R$ 175,00</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>▲ 24,8%</t>
+          <t>▼ 40,1%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>31</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▲ 72,2%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2797,14 +2797,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2827,33 +2827,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,7%</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▲ 24,8%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 38,5%</t>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2870,12 +2870,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2947,14 +2947,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2977,25 +2977,25 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 175,00</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 201,7%</t>
+          <t>R$ 234,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,7%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>18</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▲ 38,5%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3097,14 +3097,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3127,33 +3127,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 175,00</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▲ 201,7%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3247,14 +3247,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3286,16 +3286,16 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
@@ -3320,12 +3320,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3397,14 +3397,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3436,16 +3436,16 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>4</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3470,12 +3470,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3547,14 +3547,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3582,28 +3582,28 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,8%</t>
+        <v>5</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3697,14 +3697,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3727,20 +3727,20 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>▲ 18,2%</t>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3847,14 +3847,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3877,33 +3877,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>13</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3920,12 +3920,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3997,14 +3997,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4027,25 +4027,25 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 117,00</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,4%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4147,14 +4147,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 117,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4186,24 +4186,24 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4297,14 +4297,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4330,17 +4330,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▼ 87,5%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4370,12 +4370,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4447,14 +4447,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4477,33 +4477,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 117,00</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 74,2%</t>
+        <v>1</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4597,14 +4597,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4630,22 +4630,22 @@
           <t>R$ 117,00</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,9%</t>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▲ 47,6%</t>
+          <t>▼ 74,2%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4747,14 +4747,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4777,33 +4777,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 117,00</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>▼ 46,2%</t>
+          <t>▲ 47,6%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4820,12 +4820,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4897,14 +4897,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 292,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4936,24 +4936,24 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>▲ 30,0%</t>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5047,14 +5047,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5086,11 +5086,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>39</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▲ 30,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5197,14 +5197,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5230,17 +5230,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,2%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5347,14 +5347,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5377,33 +5377,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 70,4%</t>
+        <v>15</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,2%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5420,14 +5420,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5458,8 +5458,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>0</v>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5468,39 +5470,41 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5526,22 +5530,22 @@
           <t>R$ 58,00</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 85,8%</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,9%</t>
+          <t>▼ 70,4%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
@@ -5566,12 +5570,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5639,14 +5643,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5669,33 +5673,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 409,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>▲ 249,6%</t>
+          <t>▼ 85,8%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 29,9%</t>
+          <t>▲ 14,9%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5712,14 +5716,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5742,7 +5746,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5750,10 +5754,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5762,41 +5764,39 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5819,33 +5819,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 117,00</t>
+          <t>R$ 409,00</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▲ 249,6%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,2%</t>
+        <v>47</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 29,9%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5939,14 +5939,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5969,33 +5969,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 409,00</t>
+          <t>R$ 117,00</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>▲ 40,1%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>67</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▼ 8,2%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6089,14 +6089,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6119,33 +6119,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
+          <t>R$ 409,00</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,6%</t>
+          <t>▲ 40,1%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>73</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6239,14 +6239,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6269,33 +6269,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 350,00</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,6%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▲ 253,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6389,14 +6389,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6419,33 +6419,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 350,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▼ 54,5%</t>
+          <t>▲ 253,3%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6539,14 +6539,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6569,33 +6569,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>▲ 163,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,1%</t>
+          <t>▼ 54,5%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6689,14 +6689,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6719,33 +6719,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 111,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▲ 163,1%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>33</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3,1%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6839,14 +6839,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6869,33 +6869,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 111,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▼ 38,5%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6912,14 +6912,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6942,7 +6942,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6950,8 +6950,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="n">
-        <v>0</v>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6960,39 +6962,41 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7015,33 +7019,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+        <v>16</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▼ 38,5%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7058,12 +7062,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7099,9 +7103,9 @@
       <c r="I89" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7131,14 +7135,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7170,24 +7174,24 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>▲ 10,3%</t>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7204,14 +7208,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7243,11 +7247,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7277,14 +7281,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7312,20 +7316,20 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 81,2%</t>
+        <v>32</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▲ 10,3%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
@@ -7333,7 +7337,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7350,14 +7354,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7380,7 +7384,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7388,10 +7392,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I93" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7400,41 +7402,39 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7457,33 +7457,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,0%</t>
+          <t>▲ 81,2%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7500,14 +7500,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7538,8 +7538,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="n">
-        <v>0</v>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7548,39 +7550,41 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7603,33 +7607,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 264,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>▲ 24,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>▲ 8,7%</t>
+          <t>▼ 36,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7646,12 +7650,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7719,14 +7723,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7749,25 +7753,25 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 212,00</t>
-        </is>
-      </c>
-      <c r="H98" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 264,00</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▲ 24,5%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>▲ 53,3%</t>
+        <v>25</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▲ 8,7%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
@@ -7775,7 +7779,7 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7792,12 +7796,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7865,14 +7869,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7895,33 +7899,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
+          <t>R$ 212,00</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>▼ 85,2%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>23</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▲ 53,3%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7938,14 +7942,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7968,7 +7972,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -7976,10 +7980,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I101" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
@@ -7988,41 +7990,39 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -8045,33 +8045,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 714,00</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>▼ 85,2%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8088,12 +8088,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8165,14 +8165,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 714,00</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -8204,24 +8204,24 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8315,14 +8315,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -8348,17 +8348,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8465,14 +8465,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -8495,33 +8495,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 584,00</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,1%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8615,14 +8615,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 584,00</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -8654,24 +8654,24 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8765,14 +8765,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -8804,11 +8804,11 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>▲ 45,5%</t>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8915,14 +8915,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -8948,17 +8948,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>16</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▲ 45,5%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9065,14 +9065,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -9095,33 +9095,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,1%</t>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9215,14 +9215,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -9245,7 +9245,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -9254,24 +9254,24 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,2%</t>
+        <v>8</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9288,12 +9288,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9365,14 +9365,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -9404,11 +9404,11 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
-          <t>▲ 83,3%</t>
+          <t>▼ 18,2%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9438,12 +9438,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9515,14 +9515,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -9554,11 +9554,11 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9588,12 +9588,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9665,14 +9665,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -9698,17 +9698,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,5%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9815,14 +9815,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -9845,33 +9845,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>9</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9888,12 +9888,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9965,14 +9965,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -10006,22 +10006,22 @@
       <c r="I128" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J128" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -10038,12 +10038,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10115,14 +10115,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -10148,17 +10148,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -10188,12 +10188,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10265,14 +10265,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -10295,33 +10295,33 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K132" s="2" t="inlineStr">
+      <c r="M132" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L132" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M132" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10415,14 +10415,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -10445,7 +10445,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -10467,11 +10467,11 @@
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10606,9 +10606,9 @@
       <c r="I136" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10638,12 +10638,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10715,14 +10715,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -10754,11 +10754,11 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10788,12 +10788,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10865,14 +10865,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -10904,11 +10904,11 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10938,12 +10938,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11015,14 +11015,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -11048,17 +11048,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>▼ 46,7%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -11088,12 +11088,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11165,14 +11165,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -11195,33 +11195,33 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 175,00</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
-          <t>▲ 114,3%</t>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11238,12 +11238,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11315,14 +11315,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -11345,33 +11345,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 175,00</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J146" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>15</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11388,12 +11388,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11465,14 +11465,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -11495,33 +11495,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J148" s="3" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11538,14 +11538,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -11568,7 +11568,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -11576,8 +11576,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I149" s="2" t="n">
-        <v>0</v>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
@@ -11586,39 +11588,41 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L149" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -11646,20 +11650,20 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,1%</t>
+        <v>7</v>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
@@ -11667,7 +11671,7 @@
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11684,12 +11688,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11725,9 +11729,9 @@
       <c r="I151" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11757,14 +11761,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -11787,7 +11791,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -11796,24 +11800,24 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>▲ 35,7%</t>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11830,14 +11834,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -11869,11 +11873,11 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11903,14 +11907,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -11936,17 +11940,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,7%</t>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11976,14 +11980,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12006,7 +12010,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -12014,10 +12018,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I155" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
@@ -12026,41 +12028,39 @@
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12083,33 +12083,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12203,14 +12203,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12233,7 +12233,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 55,00</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -12242,24 +12242,24 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12353,14 +12353,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12392,11 +12392,11 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>▲ 250,0%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12503,14 +12503,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12536,17 +12536,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12576,12 +12576,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12653,14 +12653,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12683,33 +12683,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J164" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12726,12 +12726,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12803,14 +12803,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12833,33 +12833,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12876,12 +12876,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12953,14 +12953,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12983,33 +12983,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -13026,82 +13026,232 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>UTD-027-BR</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Porta Talheres Extensivel Branco</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>6421065554</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>R$ 64,90</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O169"/>
+  <autoFilter ref="A1:O171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 350,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▲ 199,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>▼ 11,9%</t>
+        <v>46</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,14 +709,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -739,33 +739,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 117,00</t>
+          <t>R$ 350,00</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>▼ 59,9%</t>
+          <t>▲ 199,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 22,1%</t>
+        <v>59</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,9%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +859,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -889,33 +889,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
+          <t>R$ 117,00</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>▲ 24,8%</t>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▲ 22,9%</t>
+          <t>▼ 22,1%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,14 +1009,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1039,25 +1039,25 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▲ 303,4%</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▲ 12,9%</t>
+        <v>86</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,9%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,14 +1159,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1189,33 +1189,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 234,00</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>▼ 75,2%</t>
+          <t>▲ 303,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,1%</t>
+          <t>▲ 12,9%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1232,14 +1232,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1270,8 +1270,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1280,39 +1282,41 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1335,33 +1339,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 19,9%</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▲ 19,7%</t>
+          <t>▼ 15,1%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1378,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1419,9 +1423,9 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1451,14 +1455,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1481,29 +1485,29 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
+          <t>R$ 234,00</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>▲ 149,6%</t>
+          <t>▼ 19,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,4%</t>
+          <t>▲ 19,7%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
@@ -1524,14 +1528,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1563,11 +1567,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1597,14 +1601,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1627,33 +1631,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 117,00</t>
+          <t>R$ 292,00</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,6%</t>
+          <t>▲ 149,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 11,0%</t>
+        <v>61</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,4%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1670,14 +1674,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1700,7 +1704,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1708,10 +1712,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I17" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1720,41 +1722,39 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1777,33 +1777,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 350,00</t>
+          <t>R$ 117,00</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>▲ 49,6%</t>
+          <t>▼ 66,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 8,9%</t>
+        <v>73</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1820,12 +1820,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1897,14 +1897,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1927,33 +1927,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,7%</t>
+          <t>R$ 350,00</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▲ 34,3%</t>
+          <t>▼ 8,9%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1970,12 +1970,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2047,14 +2047,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2077,33 +2077,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 175,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 234,00</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▲ 42,6%</t>
+        <v>90</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 34,3%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2197,14 +2197,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2230,22 +2230,22 @@
           <t>R$ 175,00</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,2%</t>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▲ 11,9%</t>
+        <v>67</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 42,6%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2270,12 +2270,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2347,14 +2347,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2377,33 +2377,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 42,8%</t>
+          <t>R$ 175,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▲ 27,3%</t>
+        <v>47</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,9%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2497,14 +2497,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2527,33 +2527,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 409,00</t>
+          <t>R$ 234,00</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>▲ 133,7%</t>
+          <t>▼ 42,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▲ 6,5%</t>
+        <v>42</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 27,3%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2570,12 +2570,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2647,14 +2647,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2677,33 +2677,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 175,00</t>
+          <t>R$ 409,00</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,1%</t>
+          <t>▲ 133,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▲ 72,2%</t>
+        <v>33</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,5%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2797,14 +2797,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2827,33 +2827,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
+          <t>R$ 175,00</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>▲ 24,8%</t>
+          <t>▼ 40,1%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>31</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 72,2%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2870,12 +2870,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2947,14 +2947,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2977,33 +2977,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,7%</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,8%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▲ 38,5%</t>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3097,14 +3097,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3127,25 +3127,25 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 175,00</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▲ 201,7%</t>
+          <t>R$ 234,00</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,7%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>18</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 38,5%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3247,14 +3247,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3277,33 +3277,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 175,00</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 201,7%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3397,14 +3397,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3436,16 +3436,16 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
@@ -3470,12 +3470,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3547,14 +3547,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3586,16 +3586,16 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>4</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3697,14 +3697,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3732,28 +3732,28 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 30,8%</t>
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3847,14 +3847,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3877,20 +3877,20 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>▲ 18,2%</t>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3920,12 +3920,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3997,14 +3997,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4027,33 +4027,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>13</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4147,14 +4147,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4177,25 +4177,25 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 117,00</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,4%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4297,14 +4297,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 117,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4336,24 +4336,24 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4370,12 +4370,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4447,14 +4447,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4480,17 +4480,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>▼ 87,5%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4597,14 +4597,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4627,33 +4627,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 117,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 74,2%</t>
+        <v>1</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4747,14 +4747,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4780,22 +4780,22 @@
           <t>R$ 117,00</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 59,9%</t>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>▲ 47,6%</t>
+          <t>▼ 74,2%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4820,12 +4820,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4897,14 +4897,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4927,33 +4927,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 117,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>▼ 46,2%</t>
+          <t>▲ 47,6%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5047,14 +5047,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 292,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5086,24 +5086,24 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▲ 30,0%</t>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5197,14 +5197,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5236,11 +5236,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>39</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 30,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5347,14 +5347,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5380,17 +5380,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,2%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5420,12 +5420,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5497,14 +5497,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5527,33 +5527,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 70,4%</t>
+        <v>15</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,2%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5570,14 +5570,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5608,8 +5608,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>0</v>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5618,39 +5620,41 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5676,22 +5680,22 @@
           <t>R$ 58,00</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 85,8%</t>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▲ 14,9%</t>
+          <t>▼ 70,4%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
@@ -5716,12 +5720,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5789,14 +5793,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5819,33 +5823,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 409,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>▲ 249,6%</t>
+          <t>▼ 85,8%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>▼ 29,9%</t>
+          <t>▲ 14,9%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5862,14 +5866,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5892,7 +5896,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5900,10 +5904,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5912,41 +5914,39 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5969,33 +5969,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 117,00</t>
+          <t>R$ 409,00</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▲ 249,6%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 8,2%</t>
+        <v>47</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 29,9%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6089,14 +6089,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6119,33 +6119,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 409,00</t>
+          <t>R$ 117,00</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>▲ 40,1%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>67</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,2%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6239,14 +6239,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6269,33 +6269,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
+          <t>R$ 409,00</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,6%</t>
+          <t>▲ 40,1%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>73</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6389,14 +6389,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6419,33 +6419,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 350,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,6%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▲ 253,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6539,14 +6539,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6569,33 +6569,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 350,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>▼ 54,5%</t>
+          <t>▲ 253,3%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6689,14 +6689,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6719,33 +6719,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>▲ 163,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▲ 3,1%</t>
+          <t>▼ 54,5%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6839,14 +6839,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6869,33 +6869,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 111,00</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 163,1%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>33</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,1%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6989,14 +6989,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7019,33 +7019,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 111,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>▼ 38,5%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7062,14 +7062,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7092,7 +7092,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7100,8 +7100,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="n">
-        <v>0</v>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
@@ -7110,39 +7112,41 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7165,33 +7169,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+        <v>16</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 38,5%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7208,12 +7212,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7249,9 +7253,9 @@
       <c r="I91" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7281,14 +7285,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7320,24 +7324,24 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>▲ 10,3%</t>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7354,14 +7358,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7393,11 +7397,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7427,14 +7431,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7462,20 +7466,20 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▲ 81,2%</t>
+        <v>32</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,3%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
@@ -7483,7 +7487,7 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7500,14 +7504,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7530,7 +7534,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7538,10 +7542,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I95" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7550,41 +7552,39 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7607,33 +7607,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>▼ 36,0%</t>
+          <t>▲ 81,2%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7650,14 +7650,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7680,7 +7680,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7688,8 +7688,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="n">
-        <v>0</v>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -7698,39 +7700,41 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7753,33 +7757,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 264,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>▲ 24,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>▲ 8,7%</t>
+          <t>▼ 36,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7796,12 +7800,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7869,14 +7873,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7899,25 +7903,25 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 212,00</t>
-        </is>
-      </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 264,00</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,5%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▲ 53,3%</t>
+        <v>25</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,7%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
@@ -7925,7 +7929,7 @@
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7942,12 +7946,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8015,14 +8019,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -8045,33 +8049,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
+          <t>R$ 212,00</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>▼ 85,2%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>23</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▲ 53,3%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8088,14 +8092,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -8118,7 +8122,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -8126,10 +8130,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I103" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
@@ -8138,41 +8140,39 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -8195,33 +8195,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 714,00</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,2%</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8315,14 +8315,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -8345,7 +8345,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 714,00</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8354,24 +8354,24 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8465,14 +8465,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -8498,17 +8498,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H108" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8615,14 +8615,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -8645,33 +8645,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 584,00</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>▼ 57,1%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8765,14 +8765,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -8795,7 +8795,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 584,00</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -8804,24 +8804,24 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J112" s="4" t="inlineStr">
-        <is>
-          <t>▼ 12,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8915,14 +8915,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -8954,11 +8954,11 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>▲ 45,5%</t>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9065,14 +9065,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -9098,17 +9098,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H116" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>16</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 45,5%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9215,14 +9215,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -9245,33 +9245,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>▼ 11,1%</t>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9288,12 +9288,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9365,14 +9365,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -9404,24 +9404,24 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,2%</t>
+        <v>8</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9438,12 +9438,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9515,14 +9515,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -9554,11 +9554,11 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>▲ 83,3%</t>
+          <t>▼ 18,2%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9588,12 +9588,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9665,14 +9665,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -9704,11 +9704,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9815,14 +9815,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -9848,17 +9848,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H126" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>▲ 12,5%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9888,12 +9888,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9965,14 +9965,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -9995,33 +9995,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>9</v>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -10038,12 +10038,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10115,14 +10115,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -10145,7 +10145,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -10156,22 +10156,22 @@
       <c r="I130" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J130" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10188,12 +10188,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10265,14 +10265,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -10298,17 +10298,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H132" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10415,14 +10415,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -10445,33 +10445,33 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K134" s="2" t="inlineStr">
+      <c r="M134" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L134" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M134" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10565,14 +10565,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -10595,7 +10595,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -10617,11 +10617,11 @@
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10638,12 +10638,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10715,12 +10715,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10756,9 +10756,9 @@
       <c r="I138" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J138" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10788,12 +10788,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10865,14 +10865,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -10904,11 +10904,11 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J140" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10938,12 +10938,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11015,14 +11015,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -11054,11 +11054,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -11088,12 +11088,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11165,14 +11165,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -11198,17 +11198,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H144" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
-          <t>▼ 46,7%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11238,12 +11238,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11315,14 +11315,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -11345,33 +11345,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 175,00</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>▲ 114,3%</t>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11388,12 +11388,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11465,14 +11465,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -11495,33 +11495,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H148" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 175,00</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J148" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>15</v>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11538,12 +11538,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11615,14 +11615,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -11645,33 +11645,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J150" s="4" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11688,14 +11688,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -11726,8 +11726,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I151" s="2" t="n">
-        <v>0</v>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
@@ -11736,39 +11738,41 @@
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L151" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -11796,20 +11800,20 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>▼ 21,1%</t>
+        <v>7</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
@@ -11817,7 +11821,7 @@
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11834,12 +11838,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11875,9 +11879,9 @@
       <c r="I153" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11907,14 +11911,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -11937,7 +11941,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -11946,24 +11950,24 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>▲ 35,7%</t>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11980,14 +11984,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12019,11 +12023,11 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -12053,14 +12057,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12086,17 +12090,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H156" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,7%</t>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -12126,14 +12130,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12156,7 +12160,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -12164,10 +12168,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I157" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
@@ -12176,41 +12178,39 @@
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12233,33 +12233,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12353,14 +12353,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12383,7 +12383,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 55,00</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -12392,24 +12392,24 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12503,14 +12503,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12542,11 +12542,11 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>▲ 250,0%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12576,12 +12576,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12653,14 +12653,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12686,17 +12686,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H164" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12726,12 +12726,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12803,14 +12803,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12833,33 +12833,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J166" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12876,12 +12876,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12953,14 +12953,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12983,33 +12983,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H168" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J168" s="4" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -13026,12 +13026,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13103,14 +13103,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -13133,33 +13133,33 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13176,82 +13176,232 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>UTD-027-BR</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>Porta Talheres Extensivel Branco</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>6421065554</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>R$ 64,90</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O171"/>
+  <autoFilter ref="A1:O173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,0%</t>
+          <t>▲ 19,6%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,14 +709,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -739,33 +739,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 350,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>▲ 199,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,9%</t>
+        <v>46</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 22,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +859,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -889,33 +889,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 117,00</t>
+          <t>R$ 350,00</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>▼ 59,9%</t>
+          <t>▲ 199,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,1%</t>
+        <v>59</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,9%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,14 +1009,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1039,33 +1039,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
+          <t>R$ 117,00</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>▲ 24,8%</t>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>▲ 22,9%</t>
+          <t>▼ 22,1%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,14 +1159,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1189,25 +1189,25 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 303,4%</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▲ 24,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,9%</t>
+        <v>86</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,9%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,14 +1309,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1339,33 +1339,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 234,00</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,2%</t>
+          <t>▲ 303,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,1%</t>
+          <t>▲ 12,9%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1382,14 +1382,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1420,8 +1420,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1430,39 +1432,41 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1485,33 +1489,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 19,9%</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▲ 19,7%</t>
+          <t>▼ 15,1%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1528,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1569,9 +1573,9 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1601,14 +1605,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1631,29 +1635,29 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
+          <t>R$ 234,00</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>▲ 149,6%</t>
+          <t>▼ 19,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,4%</t>
+          <t>▲ 19,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
@@ -1674,14 +1678,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1713,11 +1717,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1747,14 +1751,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1777,33 +1781,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 117,00</t>
+          <t>R$ 292,00</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,6%</t>
+          <t>▲ 149,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,0%</t>
+        <v>61</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,4%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1820,14 +1824,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1850,7 +1854,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1858,10 +1862,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I19" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1870,41 +1872,39 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -1927,33 +1927,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 350,00</t>
+          <t>R$ 117,00</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>▲ 49,6%</t>
+          <t>▼ 66,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,9%</t>
+        <v>73</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1970,12 +1970,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2047,14 +2047,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2077,33 +2077,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,7%</t>
+          <t>R$ 350,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▲ 49,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>▲ 34,3%</t>
+          <t>▼ 8,9%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2197,14 +2197,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2227,33 +2227,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 175,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 234,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 42,6%</t>
+        <v>90</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▲ 34,3%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2270,12 +2270,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2347,14 +2347,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2380,22 +2380,22 @@
           <t>R$ 175,00</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,2%</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,9%</t>
+        <v>67</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▲ 42,6%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2497,14 +2497,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2527,33 +2527,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,8%</t>
+          <t>R$ 175,00</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 27,3%</t>
+        <v>47</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▲ 11,9%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2570,12 +2570,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2647,14 +2647,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2677,33 +2677,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 409,00</t>
+          <t>R$ 234,00</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>▲ 133,7%</t>
+          <t>▼ 42,8%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,5%</t>
+        <v>42</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▲ 27,3%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2797,14 +2797,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2827,33 +2827,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 175,00</t>
+          <t>R$ 409,00</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,1%</t>
+          <t>▲ 133,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 72,2%</t>
+        <v>33</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▲ 6,5%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2870,12 +2870,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2947,14 +2947,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -2977,33 +2977,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
+          <t>R$ 175,00</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>▲ 24,8%</t>
+          <t>▼ 40,1%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>31</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▲ 72,2%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3097,14 +3097,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3127,33 +3127,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,7%</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▲ 24,8%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 38,5%</t>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3247,14 +3247,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3277,25 +3277,25 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 175,00</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 201,7%</t>
+          <t>R$ 234,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,7%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>18</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▲ 38,5%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3397,14 +3397,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3427,33 +3427,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 175,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▲ 201,7%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3470,12 +3470,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3547,14 +3547,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3586,16 +3586,16 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
@@ -3620,12 +3620,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3697,14 +3697,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3736,16 +3736,16 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>4</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3847,14 +3847,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -3882,28 +3882,28 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,8%</t>
+        <v>5</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3920,12 +3920,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3997,14 +3997,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4027,20 +4027,20 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>▲ 18,2%</t>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4147,14 +4147,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4177,33 +4177,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>13</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4297,14 +4297,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4327,25 +4327,25 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 117,00</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,4%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4370,12 +4370,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4447,14 +4447,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 117,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4486,24 +4486,24 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4597,14 +4597,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4630,17 +4630,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>▼ 87,5%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4747,14 +4747,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4777,33 +4777,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 117,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 74,2%</t>
+        <v>1</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4820,12 +4820,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4897,14 +4897,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -4930,22 +4930,22 @@
           <t>R$ 117,00</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,9%</t>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>▲ 47,6%</t>
+          <t>▼ 74,2%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5047,14 +5047,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5077,33 +5077,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 117,00</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 46,2%</t>
+          <t>▲ 47,6%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5197,14 +5197,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 292,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5236,24 +5236,24 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>▲ 30,0%</t>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5347,14 +5347,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5386,11 +5386,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>39</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▲ 30,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5420,12 +5420,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5497,14 +5497,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5530,17 +5530,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,2%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5570,12 +5570,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5647,14 +5647,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5677,33 +5677,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 70,4%</t>
+        <v>15</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,2%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5720,14 +5720,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5758,8 +5758,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
-        <v>0</v>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5768,39 +5770,41 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5826,22 +5830,22 @@
           <t>R$ 58,00</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 85,8%</t>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,9%</t>
+          <t>▼ 70,4%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
@@ -5866,12 +5870,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5939,14 +5943,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -5969,33 +5973,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 409,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>▲ 249,6%</t>
+          <t>▼ 85,8%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▼ 29,9%</t>
+          <t>▲ 14,9%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6012,14 +6016,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6042,7 +6046,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6050,10 +6054,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6062,41 +6064,39 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6119,33 +6119,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 117,00</t>
+          <t>R$ 409,00</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▲ 249,6%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,2%</t>
+        <v>47</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 29,9%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6239,14 +6239,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6269,33 +6269,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 409,00</t>
+          <t>R$ 117,00</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>▲ 40,1%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>67</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▼ 8,2%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6389,14 +6389,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6419,33 +6419,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
+          <t>R$ 409,00</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,6%</t>
+          <t>▲ 40,1%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>73</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6539,14 +6539,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6569,33 +6569,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 350,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,6%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>▲ 253,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6689,14 +6689,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6719,33 +6719,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 350,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▼ 54,5%</t>
+          <t>▲ 253,3%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6839,14 +6839,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -6869,33 +6869,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>▲ 163,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>▲ 3,1%</t>
+          <t>▼ 54,5%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6989,14 +6989,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7019,33 +7019,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 111,00</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▲ 163,1%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>33</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3,1%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7062,12 +7062,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7139,14 +7139,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7169,33 +7169,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 111,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>▼ 38,5%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7212,14 +7212,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7250,8 +7250,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="n">
-        <v>0</v>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7260,39 +7262,41 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7315,33 +7319,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+        <v>16</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▼ 38,5%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7358,12 +7362,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7399,9 +7403,9 @@
       <c r="I93" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7431,14 +7435,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7470,24 +7474,24 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>▲ 10,3%</t>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7504,14 +7508,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7543,11 +7547,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7577,14 +7581,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7612,20 +7616,20 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▲ 81,2%</t>
+        <v>32</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▲ 10,3%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
@@ -7633,7 +7637,7 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7650,14 +7654,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7680,7 +7684,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7688,10 +7692,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I97" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -7700,41 +7702,39 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7757,33 +7757,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,0%</t>
+          <t>▲ 81,2%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7800,14 +7800,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7838,8 +7838,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="n">
-        <v>0</v>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -7848,39 +7850,41 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -7903,33 +7907,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 264,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>▲ 24,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>▲ 8,7%</t>
+          <t>▼ 36,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7946,12 +7950,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8019,14 +8023,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -8049,25 +8053,25 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 212,00</t>
-        </is>
-      </c>
-      <c r="H102" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 264,00</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>▲ 24,5%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>▲ 53,3%</t>
+        <v>25</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▲ 8,7%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
@@ -8075,7 +8079,7 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8092,12 +8096,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8165,14 +8169,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -8195,33 +8199,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
+          <t>R$ 212,00</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>▼ 85,2%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>23</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▲ 53,3%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8238,14 +8242,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -8268,7 +8272,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -8276,10 +8280,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I105" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
@@ -8288,41 +8290,39 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -8345,33 +8345,33 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 714,00</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>▼ 85,2%</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J106" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8465,14 +8465,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 714,00</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -8504,24 +8504,24 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8615,14 +8615,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -8648,17 +8648,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8765,14 +8765,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -8795,33 +8795,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 584,00</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,1%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8915,14 +8915,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -8945,7 +8945,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 584,00</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -8954,24 +8954,24 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9065,14 +9065,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -9104,11 +9104,11 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>▲ 45,5%</t>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9215,14 +9215,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -9248,17 +9248,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>16</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▲ 45,5%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9288,12 +9288,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9365,14 +9365,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -9395,33 +9395,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,1%</t>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9438,12 +9438,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9515,14 +9515,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -9554,24 +9554,24 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,2%</t>
+        <v>8</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9588,12 +9588,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9665,14 +9665,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -9704,11 +9704,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>▲ 83,3%</t>
+          <t>▼ 18,2%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9815,14 +9815,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -9854,11 +9854,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9888,12 +9888,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9965,14 +9965,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -9998,17 +9998,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,5%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -10038,12 +10038,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10115,14 +10115,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -10145,33 +10145,33 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>9</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10188,12 +10188,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10265,14 +10265,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -10295,7 +10295,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -10306,22 +10306,22 @@
       <c r="I132" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J132" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10415,14 +10415,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -10448,17 +10448,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H134" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10565,14 +10565,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -10595,33 +10595,33 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K136" s="2" t="inlineStr">
+      <c r="M136" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L136" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M136" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10638,12 +10638,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10715,14 +10715,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -10767,11 +10767,11 @@
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10788,12 +10788,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10906,9 +10906,9 @@
       <c r="I140" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10938,12 +10938,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11015,14 +11015,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -11054,11 +11054,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -11088,12 +11088,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11165,14 +11165,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -11204,11 +11204,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11238,12 +11238,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11315,14 +11315,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -11348,17 +11348,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>▼ 46,7%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11388,12 +11388,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11465,14 +11465,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -11495,33 +11495,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 175,00</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
-          <t>▲ 114,3%</t>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11538,12 +11538,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11615,14 +11615,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -11645,33 +11645,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H150" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 175,00</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J150" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>15</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11688,12 +11688,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11765,14 +11765,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -11795,33 +11795,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11838,14 +11838,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -11876,8 +11876,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I153" s="2" t="n">
-        <v>0</v>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
@@ -11886,39 +11888,41 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L153" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -11946,20 +11950,20 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,1%</t>
+        <v>7</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
@@ -11967,7 +11971,7 @@
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11984,12 +11988,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12025,9 +12029,9 @@
       <c r="I155" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J155" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -12057,14 +12061,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12087,7 +12091,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -12096,24 +12100,24 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>▲ 35,7%</t>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12130,14 +12134,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12169,11 +12173,11 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -12203,14 +12207,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12236,17 +12240,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,7%</t>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12276,14 +12280,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12306,7 +12310,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12314,10 +12318,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I159" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
@@ -12326,41 +12328,39 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12383,33 +12383,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12503,14 +12503,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12533,7 +12533,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 55,00</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -12542,24 +12542,24 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12576,12 +12576,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12653,14 +12653,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12692,11 +12692,11 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>▲ 250,0%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12726,12 +12726,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12803,14 +12803,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12836,17 +12836,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12876,12 +12876,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12953,14 +12953,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -12983,33 +12983,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -13026,12 +13026,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13103,14 +13103,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -13133,33 +13133,33 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H170" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J170" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13176,12 +13176,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13253,14 +13253,14 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
           <t>UTD-027-BR</t>
@@ -13283,33 +13283,33 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J172" s="4" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L172" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -13326,82 +13326,232 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>UTD-027-BR</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>Porta Talheres Extensivel Branco</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>6421065554</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>R$ 64,90</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O173"/>
+  <autoFilter ref="A1:O175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-027-BR-PORTA-TALHERES-EXTENSIVEL-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 19,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,10 +670,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -682,39 +680,37 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -739,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 117,00</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▼ 22,0%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -812,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -820,51 +816,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -889,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 350,00</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▲ 199,1%</t>
+          <t>R$ 117,00</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 11,9%</t>
+        <v>48</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,6%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -962,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -970,10 +962,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -982,39 +972,37 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1044,28 +1032,28 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>▼ 59,9%</t>
+          <t>▲ 101,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>▼ 22,1%</t>
+          <t>▲ 7,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1147,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1189,33 +1177,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▲ 24,8%</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▲ 22,9%</t>
+        <v>55</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 19,6%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1232,12 +1220,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,12 +1297,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1339,33 +1327,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>▲ 303,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▲ 12,9%</t>
+          <t>▼ 22,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1382,12 +1370,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,12 +1447,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1489,33 +1477,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 350,00</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>▼ 75,2%</t>
+          <t>▲ 199,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,1%</t>
+        <v>59</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,9%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1532,12 +1520,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1562,7 +1550,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1570,8 +1558,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1580,37 +1570,39 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1635,33 +1627,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 19,9%</t>
+          <t>R$ 117,00</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▲ 19,7%</t>
+          <t>▼ 22,1%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1678,12 +1670,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1708,7 +1700,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1716,47 +1708,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1784,30 +1780,30 @@
           <t>R$ 292,00</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▲ 149,6%</t>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,4%</t>
+          <t>▲ 22,9%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1824,12 +1820,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1854,7 +1850,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1862,8 +1858,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
-        <v>1</v>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1872,37 +1870,39 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1927,33 +1927,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 117,00</t>
+          <t>R$ 234,00</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,6%</t>
+          <t>▲ 303,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▼ 11,0%</t>
+          <t>▲ 12,9%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1970,12 +1970,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2077,33 +2077,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 350,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>▲ 49,6%</t>
+          <t>▼ 75,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▼ 8,9%</t>
+        <v>62</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,1%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2158,10 +2158,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2170,39 +2168,37 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2232,20 +2228,20 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,7%</t>
+          <t>▼ 19,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▲ 34,3%</t>
+        <v>73</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 19,7%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
@@ -2253,7 +2249,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2270,12 +2266,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2300,7 +2296,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2308,51 +2304,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2377,33 +2369,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 175,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 149,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>▲ 42,6%</t>
+          <t>▼ 16,4%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2420,12 +2412,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2450,7 +2442,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2458,10 +2450,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I27" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2470,39 +2460,37 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2527,25 +2515,25 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 175,00</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,2%</t>
+          <t>R$ 117,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▲ 11,9%</t>
+          <t>▼ 11,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
@@ -2553,7 +2541,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2570,12 +2558,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2647,12 +2635,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2677,33 +2665,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 234,00</t>
+          <t>R$ 350,00</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>▼ 42,8%</t>
+          <t>▲ 49,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>▲ 27,3%</t>
+          <t>▼ 8,9%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2720,12 +2708,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2797,12 +2785,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2827,33 +2815,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 409,00</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▲ 133,7%</t>
+          <t>R$ 234,00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▲ 6,5%</t>
+        <v>90</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 34,3%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2870,12 +2858,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2947,12 +2935,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2980,22 +2968,22 @@
           <t>R$ 175,00</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 40,1%</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▲ 72,2%</t>
+        <v>67</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 42,6%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
@@ -3003,7 +2991,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3020,12 +3008,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3097,12 +3085,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3127,33 +3115,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
+          <t>R$ 175,00</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>▲ 24,8%</t>
+          <t>▼ 25,2%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>47</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,9%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3170,12 +3158,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3247,12 +3235,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3282,28 +3270,28 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,7%</t>
+          <t>▼ 42,8%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▲ 38,5%</t>
+        <v>42</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 27,3%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3320,12 +3308,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3397,12 +3385,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3427,33 +3415,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 175,00</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▲ 201,7%</t>
+          <t>R$ 409,00</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 133,7%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>33</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,5%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3470,12 +3458,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3547,12 +3535,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3577,33 +3565,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 175,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,1%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>31</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 72,2%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3620,12 +3608,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3697,12 +3685,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3727,33 +3715,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,8%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I44" s="2" t="n">
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3770,12 +3758,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3847,12 +3835,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3877,33 +3865,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 234,00</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,7%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▲ 38,5%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3920,12 +3908,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3997,12 +3985,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4027,33 +4015,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 175,00</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 201,7%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>▼ 30,8%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4070,12 +4058,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4147,12 +4135,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4177,33 +4165,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▲ 18,2%</t>
+        <v>12</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4220,12 +4208,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4297,12 +4285,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4330,22 +4318,22 @@
           <t>R$ 58,00</t>
         </is>
       </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,4%</t>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▲ 22,2%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
@@ -4353,7 +4341,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4370,12 +4358,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4447,12 +4435,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4477,25 +4465,25 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 117,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▲ 350,0%</t>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
@@ -4503,7 +4491,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4520,12 +4508,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4597,12 +4585,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4627,7 +4615,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4636,11 +4624,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4653,7 +4641,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4670,12 +4658,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4747,12 +4735,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4780,17 +4768,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr">
+      <c r="H58" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>▼ 87,5%</t>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4820,12 +4808,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4897,12 +4885,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4927,33 +4915,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 117,00</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,4%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>▼ 74,2%</t>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4970,12 +4958,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5047,12 +5035,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5080,30 +5068,30 @@
           <t>R$ 117,00</t>
         </is>
       </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>▼ 59,9%</t>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▲ 47,6%</t>
+        <v>9</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5120,12 +5108,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5197,12 +5185,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5227,7 +5215,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5236,24 +5224,24 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>▼ 46,2%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5270,12 +5258,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5347,12 +5335,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5380,17 +5368,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▲ 30,0%</t>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5420,12 +5408,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5497,12 +5485,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5527,33 +5515,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 117,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 74,2%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5570,12 +5558,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5647,12 +5635,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5677,33 +5665,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 117,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,2%</t>
+          <t>▲ 47,6%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5720,12 +5708,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5797,12 +5785,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5827,33 +5815,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 292,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 70,4%</t>
+        <v>21</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,2%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5870,12 +5858,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5900,7 +5888,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5908,8 +5896,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>0</v>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5918,37 +5908,39 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5973,33 +5965,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 85,8%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▲ 14,9%</t>
+        <v>39</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 30,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6016,12 +6008,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6046,7 +6038,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6054,8 +6046,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>0</v>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6064,37 +6058,39 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6119,33 +6115,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 409,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▲ 249,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▼ 29,9%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6162,12 +6158,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6239,12 +6235,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6269,33 +6265,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 117,00</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▼ 8,2%</t>
+        <v>15</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,2%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6312,12 +6308,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6389,12 +6385,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6419,33 +6415,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 409,00</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▲ 40,1%</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>16</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 70,4%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6462,12 +6458,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6492,7 +6488,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6500,10 +6496,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6512,39 +6506,37 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6569,33 +6561,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,6%</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,8%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 14,9%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6612,12 +6604,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6642,7 +6634,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6650,10 +6642,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6662,39 +6652,37 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6719,33 +6707,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 350,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 409,00</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 249,6%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▲ 253,3%</t>
+          <t>▼ 29,9%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6762,12 +6750,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6839,12 +6827,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6869,33 +6857,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 117,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▼ 54,5%</t>
+        <v>67</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,2%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6912,12 +6900,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6989,12 +6977,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7019,33 +7007,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 292,00</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>▲ 163,1%</t>
+          <t>R$ 409,00</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,1%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▲ 3,1%</t>
+        <v>73</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7062,12 +7050,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7139,12 +7127,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7169,33 +7157,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 111,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,6%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7212,12 +7200,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7289,12 +7277,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7319,33 +7307,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 350,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>▼ 38,5%</t>
+          <t>▲ 253,3%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7362,12 +7350,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7392,7 +7380,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7400,8 +7388,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="n">
-        <v>0</v>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7410,37 +7400,39 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7465,33 +7457,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+        <v>15</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 54,5%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7508,12 +7500,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7538,7 +7530,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7546,47 +7538,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7611,33 +7607,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 292,00</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 163,1%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▲ 10,3%</t>
+        <v>33</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,1%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7654,12 +7650,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7684,7 +7680,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7692,8 +7688,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="n">
-        <v>1</v>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -7702,37 +7700,39 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
+          <t>R$ 111,00</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -7766,16 +7766,16 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▲ 81,2%</t>
+        <v>32</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7910,7 +7910,7 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H100" s="4" t="inlineStr">
+      <c r="H100" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -7918,9 +7918,9 @@
       <c r="I100" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>▼ 36,0%</t>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 38,5%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8023,12 +8023,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8053,33 +8053,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 264,00</t>
-        </is>
-      </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>▲ 24,5%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>▲ 8,7%</t>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8137,9 +8137,9 @@
       <c r="I103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8199,33 +8199,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 212,00</t>
-        </is>
-      </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▲ 53,3%</t>
+        <v>32</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,3%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8242,12 +8242,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8281,7 +8281,7 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
@@ -8315,12 +8315,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8348,22 +8348,22 @@
           <t>R$ 106,00</t>
         </is>
       </c>
-      <c r="H106" s="4" t="inlineStr">
-        <is>
-          <t>▼ 85,2%</t>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>29</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>▲ 81,2%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8465,12 +8465,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8495,33 +8495,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 714,00</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 36,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -8576,10 +8576,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I109" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
@@ -8588,39 +8586,37 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8645,33 +8641,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 264,00</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,5%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 8,7%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8688,12 +8684,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8718,7 +8714,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -8726,10 +8722,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I111" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
@@ -8738,39 +8732,37 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8795,33 +8787,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 212,00</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>23</v>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 53,3%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8838,12 +8830,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8868,7 +8860,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -8876,10 +8868,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I113" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
@@ -8888,39 +8878,37 @@
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8945,33 +8933,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 584,00</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,2%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>15</v>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8988,12 +8976,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9065,12 +9053,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9095,7 +9083,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 714,00</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -9104,24 +9092,24 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>▼ 12,5%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9138,12 +9126,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9215,12 +9203,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9254,11 +9242,11 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>▲ 45,5%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9288,12 +9276,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9365,12 +9353,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9398,17 +9386,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H120" s="4" t="inlineStr">
+      <c r="H120" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>7</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9438,12 +9426,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9515,12 +9503,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9545,7 +9533,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 584,00</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -9554,16 +9542,16 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J122" s="4" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+        <v>6</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
@@ -9571,7 +9559,7 @@
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9588,12 +9576,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9665,12 +9653,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9704,11 +9692,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,2%</t>
+        <v>14</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9738,12 +9726,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9815,12 +9803,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9854,11 +9842,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>▲ 83,3%</t>
+        <v>16</v>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>▲ 45,5%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9888,12 +9876,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9965,12 +9953,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -9998,17 +9986,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -10038,12 +10026,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10115,12 +10103,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10145,33 +10133,33 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H130" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 58,00</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>▲ 12,5%</t>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10188,12 +10176,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10265,12 +10253,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10295,7 +10283,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -10304,24 +10292,24 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>9</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,2%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10338,12 +10326,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10415,12 +10403,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10454,11 +10442,11 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J134" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>11</v>
+      </c>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10488,12 +10476,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10565,12 +10553,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10598,17 +10586,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H136" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10638,12 +10626,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10715,12 +10703,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10745,33 +10733,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,5%</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K138" s="2" t="inlineStr">
+      <c r="M138" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L138" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M138" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10788,12 +10776,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10865,12 +10853,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10895,7 +10883,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -10904,24 +10892,24 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10938,12 +10926,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11015,12 +11003,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11054,11 +11042,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J142" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -11088,12 +11076,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11165,12 +11153,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11198,17 +11186,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11238,12 +11226,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11315,12 +11303,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11345,7 +11333,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -11354,11 +11342,11 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J146" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11367,11 +11355,11 @@
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11388,12 +11376,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11465,12 +11453,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11498,17 +11486,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H148" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J148" s="4" t="inlineStr">
-        <is>
-          <t>▼ 46,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11538,12 +11526,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11615,12 +11603,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11645,7 +11633,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 175,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -11654,24 +11642,24 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>▲ 114,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11688,12 +11676,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11765,12 +11753,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11798,17 +11786,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H152" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J152" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>9</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11838,12 +11826,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11915,12 +11903,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -11945,33 +11933,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
-          <t>▼ 53,3%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11988,12 +11976,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12018,7 +12006,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -12026,8 +12014,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I155" s="2" t="n">
-        <v>0</v>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
@@ -12036,37 +12026,39 @@
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L155" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12091,33 +12083,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 58,00</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>▼ 21,1%</t>
+        <v>8</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12134,12 +12126,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12164,7 +12156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -12172,47 +12164,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I157" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J157" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L157" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12237,7 +12233,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 175,00</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -12246,24 +12242,24 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>▲ 35,7%</t>
+        <v>15</v>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12280,12 +12276,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12310,7 +12306,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12318,8 +12314,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I159" s="2" t="n">
-        <v>1</v>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
@@ -12328,37 +12326,39 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L159" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12386,17 +12386,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H160" s="4" t="inlineStr">
+      <c r="H160" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12503,12 +12503,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12533,25 +12533,25 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
@@ -12559,7 +12559,7 @@
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12576,12 +12576,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -12614,10 +12614,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I163" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
@@ -12626,39 +12624,37 @@
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12683,7 +12679,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 58,00</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -12692,24 +12688,24 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J164" s="4" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>15</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12726,12 +12722,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12756,7 +12752,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -12764,51 +12760,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12842,11 +12834,11 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▲ 250,0%</t>
+        <v>19</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12876,12 +12868,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12906,7 +12898,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -12914,10 +12906,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I167" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
@@ -12926,39 +12916,37 @@
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L167" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -12986,17 +12974,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H168" s="4" t="inlineStr">
+      <c r="H168" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J168" s="4" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -13026,12 +13014,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13103,12 +13091,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -13142,16 +13130,16 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>15</v>
+      </c>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
@@ -13159,7 +13147,7 @@
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13176,12 +13164,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13253,12 +13241,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13286,17 +13274,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H172" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J172" s="4" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -13326,12 +13314,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13403,12 +13391,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -13433,7 +13421,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -13442,24 +13430,24 @@
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J174" s="4" t="inlineStr">
+        <is>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L174" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
@@ -13476,82 +13464,682 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H176" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J176" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H180" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>6421065554</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>UTD-027-BR</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>Porta Talheres Extensivel Branco</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>6421040394</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>UTD-027-BR</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Porta Talheres Extensivel Branco</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>6421065554</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>R$ 64,90</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O175" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 64,90</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O175"/>
+  <autoFilter ref="A1:O183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>